--- a/stories/arbres/ATOM-TMP.SEM.002-07.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Eugénie est dans le salon. Maman accroche un calendrier. Maman dit : lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Eugénie reste à la maison. Elle joue avec maman. Samedi, Eugénie reste aussi. Dimanche encore. Maman dit : samedi et dimanche, c'est le week-end. Eugénie touche mercredi. Elle touche samedi. Elle touche dimanche.</t>
+          <t>Eugénie est dans le salon. Maman accroche un calendrier. Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Eugénie reste à la maison. Elle joue avec maman. Samedi, Eugénie reste aussi. Dimanche encore. Samedi et dimanche, c'est le week-end. Eugénie touche mercredi. Elle touche samedi. Elle touche dimanche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Eugénie est dans le salon. Maman accroche un calendrier.
+maman|Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Eugénie reste à la maison. Elle joue avec maman. Samedi, Eugénie reste aussi. Dimanche encore.
+maman|Samedi et dimanche, c'est le week-end.
+narrateur|Eugénie touche mercredi. Elle touche samedi. Elle touche dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Eugénie est à la maison le mercredi. Quels autres jours aussi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Eugénie a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le crayon. Eugénie dessine.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.002-07.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 narrateur|Eugénie touche mercredi. Elle touche samedi. Elle touche dimanche.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Eugénie est à la maison le mercredi. Quels autres jours aussi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Eugénie a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Maman range le crayon. Eugénie dessine.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SEM.002-07.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eugénie nomme mercredi et le week-end</t>
+          <t>La vapeur et le marché</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou veut une soupe orange. Mercredi, une carotte roule sous la table. Elle la rattrape. Dimanche, week-end, le marché sent les mêmes carottes.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Eugénie est dans le salon. Maman accroche un calendrier. Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Eugénie reste à la maison. Elle joue avec maman. Samedi, Eugénie reste aussi. Dimanche encore. Samedi et dimanche, c'est le week-end. Eugénie touche mercredi. Elle touche samedi. Elle touche dimanche.</t>
+          <t>La vapeur de soupe embue la vitre. Un rond de jour flotte dans la buée. Ça sent la carotte chaude. C'est mercredi, Chouchou. Pas d'école. On fait la soupe ? Oui. Tu peux la carotte. La grande. Chouchou prend une carotte mouillée. Elle glisse. Elle roule sous la table. Elle part ! On la cherche ? Oui. En ce moment, Chouchou se penche. Le carrelage est froid aux genoux. La carotte attend près du pied de chaise. Je l'ai. Merci. Elle voulait se cacher. Chouchou la pose dans le saladier. L'eau fait un petit ploc. On coupe ensemble. Des ronds. Des ronds orange. Les ronds tombent, mous, luisants. Mercredi, on cuisine. Dimanche, on ira au marché. Pour d'autres carottes ? Pour d'autres. Samedi et dimanche, c'est le week-end. Pas d'école. Pas d'école. Comme mercredi. La casserole chante un peu. La vapeur sent plus fort. Je souffle. Pas trop près. On goûte plus tard. Chouchou trace un soleil dans la buée. Le doigt laisse une vitre claire. Tu vois le jardin ? Un peu. Samedi, on finira le bol. Dimanche, le marché. J'attends dimanche. Une goutte coule sur la carotte retrouvée. Elle brille, toute propre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Eugénie est dans le salon. Maman accroche un calendrier. Maman dit : lundi, mardi, jeudi, vendredi, c'est l'école. &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;, Eugénie reste à la maison. Elle joue avec maman. Samedi, Eugénie reste aussi. Dimanche encore. Maman dit : samedi et dimanche, c'est le week-end. Eugénie touche mercredi. Elle touche samedi. Elle touche dimanche.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vapeur de soupe embue la vitre. Un rond de jour flotte dans la buée. Ça sent la carotte chaude. C'est mercredi, Chouchou. Pas d'école. On fait la soupe ? Oui. Tu peux la carotte. La grande. Chouchou prend une carotte mouillée. Elle glisse. Elle roule sous la table. Elle part ! On la cherche ? Oui. En ce moment, Chouchou se penche. Le carrelage est froid aux genoux. La carotte attend près du pied de chaise. Je l'ai. Merci. Elle voulait se cacher. Chouchou la pose dans le saladier. L'eau fait un petit ploc. On coupe ensemble. Des ronds. Des ronds orange. Les ronds tombent, mous, luisants. Mercredi, on cuisine. Dimanche, on ira au marché. Pour d'autres carottes ? Pour d'autres. Samedi et dimanche, c'est le week-end. Pas d'école. Pas d'école. Comme mercredi. La casserole chante un peu. La vapeur sent plus fort. Je souffle. Pas trop près. On goûte plus tard. Chouchou trace un soleil dans la buée. Le doigt laisse une vitre claire. Tu vois le jardin ? Un peu. Samedi, on finira le bol. Dimanche, le marché. J'attends dimanche. Une goutte coule sur la carotte retrouvée. Elle brille, toute propre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Eugénie est dans le salon. Maman accroche un calendrier.
-maman|Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Eugénie reste à la maison. Elle joue avec maman. Samedi, Eugénie reste aussi. Dimanche encore.
+          <t>narrateur|La vapeur de soupe embue la vitre.
+narrateur|Un rond de jour flotte dans la buée.
+narrateur|Ça sent la carotte chaude.
+maman|C'est mercredi, Chouchou.
+maman|Pas d'école.
+enfant-f|On fait la soupe ?
+maman|Oui.
+maman|Tu peux la carotte.
+enfant-f|La grande.
+narrateur|Chouchou prend une carotte mouillée.
+narrateur|Elle glisse.
+narrateur|Elle roule sous la table.
+enfant-f|Elle part !
+maman|On la cherche ?
+enfant-f|Oui.
+narrateur|En ce moment, Chouchou se penche.
+narrateur|Le carrelage est froid aux genoux.
+narrateur|La carotte attend près du pied de chaise.
+enfant-f|Je l'ai.
+maman|Merci.
+maman|Elle voulait se cacher.
+narrateur|Chouchou la pose dans le saladier.
+narrateur|L'eau fait un petit ploc.
+maman|On coupe ensemble.
+enfant-f|Des ronds.
+maman|Des ronds orange.
+narrateur|Les ronds tombent, mous, luisants.
+maman|Mercredi, on cuisine.
+maman|Dimanche, on ira au marché.
+enfant-f|Pour d'autres carottes ?
+maman|Pour d'autres.
 maman|Samedi et dimanche, c'est le week-end.
-narrateur|Eugénie touche mercredi. Elle touche samedi. Elle touche dimanche.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|Pas d'école.
+maman|Pas d'école.
+maman|Comme mercredi.
+narrateur|La casserole chante un peu.
+narrateur|La vapeur sent plus fort.
+enfant-f|Je souffle.
+maman|Pas trop près.
+maman|On goûte plus tard.
+narrateur|Chouchou trace un soleil dans la buée.
+narrateur|Le doigt laisse une vitre claire.
+maman|Tu vois le jardin ?
+enfant-f|Un peu.
+maman|Samedi, on finira le bol.
+maman|Dimanche, le marché.
+enfant-f|J'attends dimanche.
+narrateur|Une goutte coule sur la carotte retrouvée.
+narrateur|Elle brille, toute propre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1399,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Eugénie est à la maison le mercredi. Quels autres jours aussi ?</t>
+          <t>Quels autres jours, comme mercredi, sans l'école ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Eugénie est à la maison le &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;. Quels autres jours aussi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Quels autres jours, comme mercredi, sans l'école ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,7 +1419,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>samedi | dimanche | week-end | mercredi</t>
+          <t>week-end | weekend | samedi | dimanche | le week-end | mercredi</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1427,7 +1483,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1503,10 +1559,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Eugénie est à la maison le mercredi. Quels autres jours aussi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Quels autres jours, comme mercredi, sans l'école ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1531,12 +1586,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Eugénie a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
+          <t>Chouchou essuie ses genoux du plat de la main. Samedi. Dimanche. Oui. C'est le week-end. Dimanche, les carottes du marché. Comme celle-là. Comme celle que tu as rattrapée. La soupe tourne, orange, épaisse. Une bulle éclate, tout doux. Tu as cherché sous la table. Bravo. Elle roulait. Et tu l'as eue. On goûte ? Oui, maman. La cuillère est chaude au bord des lèvres. La carotte a un goût sucré.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Eugénie a nommé &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;. Elle a nommé samedi et dimanche. C'est le week-end.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou essuie ses genoux du plat de la main. Samedi. Dimanche. Oui. C'est le week-end. Dimanche, les carottes du marché. Comme celle-là. Comme celle que tu as rattrapée. La soupe tourne, orange, épaisse. Une bulle éclate, tout doux. Tu as cherché sous la table. Bravo. Elle roulait. Et tu l'as eue. On goûte ? Oui, maman. La cuillère est chaude au bord des lèvres. La carotte a un goût sucré.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1599,7 +1654,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1675,10 +1730,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Eugénie a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Chouchou essuie ses genoux du plat de la main.
+enfant-f|Samedi.
+enfant-f|Dimanche.
+maman|Oui.
+maman|C'est le week-end.
+maman|Dimanche, les carottes du marché.
+enfant-f|Comme celle-là.
+maman|Comme celle que tu as rattrapée.
+narrateur|La soupe tourne, orange, épaisse.
+narrateur|Une bulle éclate, tout doux.
+maman|Tu as cherché sous la table.
+maman|Bravo.
+enfant-f|Elle roulait.
+maman|Et tu l'as eue.
+maman|On goûte ?
+enfant-f|Oui, maman.
+narrateur|La cuillère est chaude au bord des lèvres.
+narrateur|La carotte a un goût sucré.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1703,12 +1774,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le crayon. Eugénie dessine.</t>
+          <t>Dimanche, le marché sent la terre mouillée. Une caisse de carottes fume un peu au froid. Comme la soupe. Comme mercredi. Chouchou montre une botte orange. Les fanes sont encore vertes, piquantes. Celles-là ? Celles-là. On les prend. Le sac devient lourd, froid. Pour la prochaine soupe. Pour la prochaine. C'est le week-end. Merci, maman. Merci d'avoir choisi. Une carotte dépasse du sac. Elle ne roule pas. Je la tiens. Le marché sonne de cagettes et de voix.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le crayon. Eugénie dessine.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dimanche, le marché sent la terre mouillée. Une caisse de carottes fume un peu au froid. Comme la soupe. Comme mercredi. Chouchou montre une botte orange. Les fanes sont encore vertes, piquantes. Celles-là ? Celles-là. On les prend. Le sac devient lourd, froid. Pour la prochaine soupe. Pour la prochaine. C'est le week-end. Merci, maman. Merci d'avoir choisi. Une carotte dépasse du sac. Elle ne roule pas. Je la tiens. Le marché sonne de cagettes et de voix.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1771,7 +1842,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1839,10 +1910,27 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le crayon. Eugénie dessine.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Dimanche, le marché sent la terre mouillée.
+narrateur|Une caisse de carottes fume un peu au froid.
+enfant-f|Comme la soupe.
+maman|Comme mercredi.
+narrateur|Chouchou montre une botte orange.
+narrateur|Les fanes sont encore vertes, piquantes.
+maman|Celles-là ?
+enfant-f|Celles-là.
+maman|On les prend.
+narrateur|Le sac devient lourd, froid.
+enfant-f|Pour la prochaine soupe.
+maman|Pour la prochaine.
+maman|C'est le week-end.
+enfant-f|Merci, maman.
+maman|Merci d'avoir choisi.
+narrateur|Une carotte dépasse du sac.
+narrateur|Elle ne roule pas.
+enfant-f|Je la tiens.
+narrateur|Le marché sonne de cagettes et de voix.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a les carottes. Comme mercredi, en plus grand. Les fanes piquent un peu le poignet. Le sac sent la terre et le sucré. Une vapeur de soupe semble encore là.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a les carottes. Comme mercredi, en plus grand. Les fanes piquent un peu le poignet. Le sac sent la terre et le sucré. Une vapeur de soupe semble encore là.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1928,14 +2016,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2007,10 +2095,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|On a les carottes.
+maman|Comme mercredi, en plus grand.
+narrateur|Les fanes piquent un peu le poignet.
+narrateur|Le sac sent la terre et le sucré.
+narrateur|Une vapeur de soupe semble encore là.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2158,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.002-07.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>cuisine mercredi, marché dimanche</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Eugénie, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
